--- a/review_appointment_forms/009_hair_specialist_review_appointment_form--review_appointment_forms.xlsx
+++ b/review_appointment_forms/009_hair_specialist_review_appointment_form--review_appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'consultation'}</t>
+          <t>consultation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Consultation'}</t>
+          <t>Consultation</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'follow-up_consultation'}</t>
+          <t>follow-up_consultation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Follow-up Consultation'}</t>
+          <t>Follow-up Consultation</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'hair_specialist'}</t>
+          <t>hair_specialist</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Hair Specialist'}</t>
+          <t>Hair Specialist</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'assistant'}</t>
+          <t>assistant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'Assistant'}</t>
+          <t>Assistant</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'value':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'value': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
